--- a/src/docs/Montgomery2020_PM25_Mucociliary_SOMA.xlsx
+++ b/src/docs/Montgomery2020_PM25_Mucociliary_SOMA.xlsx
@@ -879,7 +879,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>log2 fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>percent (UO:0000187)</t>
+          <t>UO:0000187</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>log2 fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>ug/cm2 (UO:0000274)</t>
+          <t>UO:0000274</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>hour (UO:0000032)</t>
+          <t>UO:0000032</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>ug/cm2 (UO:0000274)</t>
+          <t>UO:0000274</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>hour (UO:0000032)</t>
+          <t>UO:0000032</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>ug/cm2 (UO:0000274)</t>
+          <t>UO:0000274</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>hour (UO:0000032)</t>
+          <t>UO:0000032</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>nasal cavity (UBERON:0001707)</t>
+          <t>UBERON:0001707</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>nasal cavity (UBERON:0001707)</t>
+          <t>UBERON:0001707</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>nasal cavity (UBERON:0001707)</t>
+          <t>UBERON:0001707</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>log2 fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>log2 fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>log2 fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>log2 fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>log2 fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>log2 fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>log2 fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>log2 fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>log2 fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr"/>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>log2 fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>log2 fold change (UO:0000193)</t>
+          <t>UO:0000193</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
